--- a/data/trans_dic/P16A10-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,99</t>
+          <t>2,93; 7,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 8,68</t>
+          <t>2,8; 8,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,31</t>
+          <t>2,43; 7,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 8,12</t>
+          <t>3,54; 8,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,52</t>
+          <t>1,61; 6,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,11</t>
+          <t>3,09; 8,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,0</t>
+          <t>2,3; 7,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,47</t>
+          <t>2,48; 6,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,29</t>
+          <t>2,65; 6,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,6</t>
+          <t>3,66; 7,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,4</t>
+          <t>2,94; 6,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,49</t>
+          <t>3,4; 6,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,56</t>
+          <t>4,79; 9,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,94</t>
+          <t>2,44; 6,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,44</t>
+          <t>5,01; 9,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,5</t>
+          <t>4,14; 8,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,41</t>
+          <t>3,53; 7,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,29</t>
+          <t>3,47; 7,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,73</t>
+          <t>3,75; 7,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,24</t>
+          <t>3,4; 6,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,56</t>
+          <t>4,44; 7,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,92</t>
+          <t>3,36; 6,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,94</t>
+          <t>4,89; 8,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,06</t>
+          <t>4,25; 6,89</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,19</t>
+          <t>2,6; 7,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,48</t>
+          <t>4,03; 9,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,17</t>
+          <t>3,62; 8,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,85</t>
+          <t>4,38; 8,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,0</t>
+          <t>3,22; 8,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,7</t>
+          <t>4,04; 9,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,5</t>
+          <t>1,28; 5,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,47</t>
+          <t>5,15; 9,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,66</t>
+          <t>3,29; 6,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,55</t>
+          <t>4,72; 8,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,99</t>
+          <t>2,76; 6,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,14</t>
+          <t>5,25; 8,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,4</t>
+          <t>2,23; 6,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,52</t>
+          <t>4,83; 10,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,68</t>
+          <t>4,59; 9,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,16</t>
+          <t>4,07; 8,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 8,6</t>
+          <t>3,81; 8,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,63</t>
+          <t>3,23; 7,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,74</t>
+          <t>7,43; 14,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,3</t>
+          <t>2,31; 6,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,61</t>
+          <t>3,62; 6,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,11</t>
+          <t>4,7; 8,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 11,13</t>
+          <t>6,65; 11,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,52</t>
+          <t>3,33; 6,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,0</t>
+          <t>4,9; 12,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 10,04</t>
+          <t>3,64; 10,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,5</t>
+          <t>3,21; 9,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,6</t>
+          <t>1,81; 5,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 8,94</t>
+          <t>2,46; 8,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 10,11</t>
+          <t>3,49; 10,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,81</t>
+          <t>2,09; 8,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,35</t>
+          <t>2,68; 6,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 9,01</t>
+          <t>4,26; 9,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,92</t>
+          <t>4,16; 8,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,55</t>
+          <t>3,32; 7,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,35</t>
+          <t>2,78; 5,44</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 9,88</t>
+          <t>4,23; 9,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,87</t>
+          <t>3,84; 9,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,08</t>
+          <t>2,74; 8,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,44</t>
+          <t>4,41; 8,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,49</t>
+          <t>4,22; 10,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,14; 10,41</t>
+          <t>4,09; 10,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,73; 11,8</t>
+          <t>4,71; 11,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,55</t>
+          <t>3,72; 7,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,21</t>
+          <t>4,72; 9,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,9</t>
+          <t>4,89; 9,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,92</t>
+          <t>4,24; 8,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,2</t>
+          <t>4,47; 7,42</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,15</t>
+          <t>2,92; 6,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,53</t>
+          <t>4,81; 8,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,31</t>
+          <t>3,85; 7,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,31</t>
+          <t>4,0; 7,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,66</t>
+          <t>3,38; 6,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,29</t>
+          <t>2,34; 5,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,52</t>
+          <t>2,29; 5,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,07</t>
+          <t>1,99; 6,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,87</t>
+          <t>3,53; 5,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,37</t>
+          <t>3,78; 6,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,88</t>
+          <t>3,43; 5,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,01</t>
+          <t>2,9; 6,13</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,55</t>
+          <t>4,32; 7,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,72</t>
+          <t>1,99; 4,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,73</t>
+          <t>4,88; 8,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,75</t>
+          <t>1,83; 6,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,66</t>
+          <t>4,02; 7,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,17</t>
+          <t>2,4; 5,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,02</t>
+          <t>3,78; 6,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,2</t>
+          <t>4,68; 7,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,99</t>
+          <t>4,59; 7,04</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,58</t>
+          <t>2,52; 4,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,29</t>
+          <t>4,67; 7,21</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,37</t>
+          <t>3,06; 6,3</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,27</t>
+          <t>4,69; 6,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,07</t>
+          <t>4,54; 6,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,78</t>
+          <t>5,14; 6,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,18</t>
+          <t>3,92; 6,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,04</t>
+          <t>4,57; 6,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,55</t>
+          <t>4,13; 5,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,18</t>
+          <t>4,62; 6,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,94; 5,53</t>
+          <t>4,0; 5,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 5,88</t>
+          <t>4,84; 5,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 5,55</t>
+          <t>4,48; 5,57</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,27</t>
+          <t>5,15; 6,26</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,46; 5,71</t>
+          <t>4,5; 5,74</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8145; 21805</t>
+          <t>7990; 21196</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8118; 25264</t>
+          <t>8160; 25055</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7198; 21489</t>
+          <t>7136; 20655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10678; 25282</t>
+          <t>11015; 25453</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4013; 17005</t>
+          <t>4189; 16737</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8905; 25893</t>
+          <t>8787; 25071</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7091; 23097</t>
+          <t>6632; 21972</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7174; 18748</t>
+          <t>7172; 19633</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14715; 33585</t>
+          <t>14156; 33222</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20285; 43701</t>
+          <t>21046; 44310</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17175; 37267</t>
+          <t>17151; 38015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19892; 39039</t>
+          <t>20443; 39094</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23923; 47125</t>
+          <t>23643; 47119</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11410; 30039</t>
+          <t>12316; 30436</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25163; 47460</t>
+          <t>25195; 48143</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22461; 43995</t>
+          <t>21395; 44465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17363; 37367</t>
+          <t>17800; 37536</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17933; 38046</t>
+          <t>18130; 38249</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19348; 40447</t>
+          <t>19641; 39840</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15946; 32080</t>
+          <t>17467; 32407</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45441; 75326</t>
+          <t>44314; 76667</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34691; 60820</t>
+          <t>34498; 62000</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50048; 81403</t>
+          <t>50164; 82634</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43736; 72810</t>
+          <t>43786; 71043</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8084; 22938</t>
+          <t>8305; 22646</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12318; 30624</t>
+          <t>13014; 31934</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11396; 26027</t>
+          <t>11535; 26548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13432; 27966</t>
+          <t>13835; 27723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10152; 26833</t>
+          <t>10788; 27016</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15069; 33068</t>
+          <t>13781; 33050</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4067; 18495</t>
+          <t>4309; 18950</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17935; 33051</t>
+          <t>17977; 32401</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21536; 43601</t>
+          <t>21541; 43356</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31182; 56775</t>
+          <t>31354; 56729</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18505; 39234</t>
+          <t>18061; 39947</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34247; 54132</t>
+          <t>34893; 54974</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8834; 22943</t>
+          <t>8004; 22249</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18269; 39354</t>
+          <t>18068; 40149</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16174; 35824</t>
+          <t>16970; 34846</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13393; 28644</t>
+          <t>12716; 27022</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13719; 31929</t>
+          <t>14151; 32350</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12017; 29601</t>
+          <t>12538; 30299</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28672; 57067</t>
+          <t>28790; 56691</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10684; 29955</t>
+          <t>10994; 28615</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26655; 48262</t>
+          <t>26399; 49412</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34222; 61816</t>
+          <t>35804; 61425</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50099; 84245</t>
+          <t>50352; 83845</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25829; 51367</t>
+          <t>26264; 50654</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9922; 24393</t>
+          <t>9969; 25725</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6835; 21338</t>
+          <t>7748; 22796</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7066; 22169</t>
+          <t>6772; 20095</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3191; 10005</t>
+          <t>3233; 10278</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5290; 18558</t>
+          <t>5101; 18421</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7560; 22193</t>
+          <t>7670; 22243</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4222; 17074</t>
+          <t>4564; 17646</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6032; 13246</t>
+          <t>5602; 13126</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17880; 37028</t>
+          <t>17501; 37989</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17492; 38545</t>
+          <t>17984; 38664</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15152; 32446</t>
+          <t>14257; 32540</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10760; 20721</t>
+          <t>10771; 21071</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11281; 26765</t>
+          <t>11459; 26367</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10381; 27043</t>
+          <t>10534; 27357</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6518; 21253</t>
+          <t>7207; 22534</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11697; 22754</t>
+          <t>11889; 23578</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11674; 29170</t>
+          <t>11742; 29938</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11557; 29045</t>
+          <t>11429; 29983</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12932; 32229</t>
+          <t>12864; 31352</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9940; 19412</t>
+          <t>9557; 19495</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26863; 50572</t>
+          <t>25933; 49440</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26480; 49230</t>
+          <t>27024; 49832</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22906; 47809</t>
+          <t>22719; 44720</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23934; 37897</t>
+          <t>23544; 39079</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17634; 37821</t>
+          <t>17955; 37044</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30898; 56562</t>
+          <t>31858; 58114</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24301; 47993</t>
+          <t>25289; 49545</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24080; 45664</t>
+          <t>24997; 45844</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>21292; 42480</t>
+          <t>21580; 43291</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16127; 36716</t>
+          <t>16228; 35366</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16599; 38182</t>
+          <t>15830; 37878</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17415; 51562</t>
+          <t>16864; 51633</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43703; 73510</t>
+          <t>44299; 73094</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53388; 86395</t>
+          <t>51282; 84949</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46060; 79246</t>
+          <t>46233; 77624</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>42166; 88595</t>
+          <t>42702; 90320</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30891; 56082</t>
+          <t>32081; 55810</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15118; 36705</t>
+          <t>15478; 36109</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>38369; 67974</t>
+          <t>37982; 66049</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17800; 62652</t>
+          <t>16955; 61690</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32012; 59999</t>
+          <t>31474; 58795</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20179; 42460</t>
+          <t>19681; 43370</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30697; 58031</t>
+          <t>31268; 56519</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33272; 51400</t>
+          <t>33421; 52136</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70317; 106724</t>
+          <t>70075; 107380</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40701; 73191</t>
+          <t>40300; 70691</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>77504; 116949</t>
+          <t>74926; 115639</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>50925; 104620</t>
+          <t>50217; 103461</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>151478; 205422</t>
+          <t>153538; 202598</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>153180; 207758</t>
+          <t>155255; 211198</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>173541; 230261</t>
+          <t>174520; 230470</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>141855; 213766</t>
+          <t>135483; 213993</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>154492; 204222</t>
+          <t>154493; 207824</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>144719; 196865</t>
+          <t>146419; 199323</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>163842; 219186</t>
+          <t>163587; 222624</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>144087; 202394</t>
+          <t>146292; 203907</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>319374; 391562</t>
+          <t>322063; 393925</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>314112; 386473</t>
+          <t>312413; 388024</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>353330; 434981</t>
+          <t>357015; 434160</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>317171; 406526</t>
+          <t>320204; 408796</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A10-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,76</t>
+          <t>2,97; 8,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,61</t>
+          <t>2,67; 8,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,03</t>
+          <t>2,4; 7,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,17</t>
+          <t>3,8; 8,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,42</t>
+          <t>1,48; 6,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,82</t>
+          <t>3,19; 8,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,61</t>
+          <t>2,29; 7,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,78</t>
+          <t>2,17; 5,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,22</t>
+          <t>2,69; 6,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,7</t>
+          <t>3,57; 7,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,53</t>
+          <t>3,08; 6,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,5</t>
+          <t>3,38; 6,14</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,56</t>
+          <t>4,49; 9,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,02</t>
+          <t>2,33; 6,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,58</t>
+          <t>4,92; 9,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 8,59</t>
+          <t>4,17; 8,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,45</t>
+          <t>3,46; 7,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,33</t>
+          <t>3,46; 7,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,62</t>
+          <t>3,84; 7,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,31</t>
+          <t>3,16; 6,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,69</t>
+          <t>4,67; 7,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,04</t>
+          <t>3,25; 5,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,06</t>
+          <t>4,79; 7,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,89</t>
+          <t>4,06; 6,64</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,1</t>
+          <t>2,56; 6,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 9,88</t>
+          <t>3,85; 9,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,33</t>
+          <t>3,3; 8,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,77</t>
+          <t>4,16; 8,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,05</t>
+          <t>3,14; 7,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,69</t>
+          <t>4,37; 9,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,63</t>
+          <t>1,23; 5,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,28</t>
+          <t>4,9; 9,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,63</t>
+          <t>3,31; 6,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,54</t>
+          <t>4,61; 8,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,1</t>
+          <t>2,81; 5,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,26</t>
+          <t>5,18; 8,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,2</t>
+          <t>2,48; 6,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,74</t>
+          <t>4,98; 10,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 9,42</t>
+          <t>4,58; 9,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,65</t>
+          <t>4,01; 8,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,71</t>
+          <t>3,64; 8,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,81</t>
+          <t>3,11; 7,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 14,64</t>
+          <t>7,46; 14,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,02</t>
+          <t>3,24; 7,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,77</t>
+          <t>3,68; 6,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,06</t>
+          <t>4,4; 7,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 11,07</t>
+          <t>6,77; 11,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,43</t>
+          <t>3,99; 7,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,65</t>
+          <t>4,74; 12,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,72</t>
+          <t>3,2; 10,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,51</t>
+          <t>3,51; 10,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,75</t>
+          <t>1,78; 5,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,87</t>
+          <t>2,64; 8,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 10,13</t>
+          <t>3,29; 10,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,07</t>
+          <t>2,04; 7,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,29</t>
+          <t>2,73; 5,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,24</t>
+          <t>4,46; 9,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,95</t>
+          <t>4,1; 8,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,57</t>
+          <t>3,16; 7,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,44</t>
+          <t>2,64; 5,29</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 9,74</t>
+          <t>3,76; 9,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,99</t>
+          <t>4,02; 9,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,56</t>
+          <t>2,8; 7,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,74</t>
+          <t>4,3; 8,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,22; 10,76</t>
+          <t>4,19; 10,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,74</t>
+          <t>4,15; 10,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,48</t>
+          <t>4,49; 12,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,58</t>
+          <t>3,87; 7,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,01</t>
+          <t>4,87; 9,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,01</t>
+          <t>4,84; 8,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,34</t>
+          <t>4,28; 8,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,42</t>
+          <t>4,44; 7,19</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,02</t>
+          <t>2,85; 5,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,77</t>
+          <t>4,8; 8,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,55</t>
+          <t>3,73; 7,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,34</t>
+          <t>4,23; 7,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,78</t>
+          <t>3,31; 6,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,1</t>
+          <t>2,28; 5,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,48</t>
+          <t>2,26; 5,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,08</t>
+          <t>4,71; 7,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,83</t>
+          <t>3,46; 5,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,26</t>
+          <t>3,94; 6,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,76</t>
+          <t>3,48; 5,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,13</t>
+          <t>4,88; 7,12</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,27 +1664,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
           <t>5,88%</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,51</t>
+          <t>4,25; 7,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,65</t>
+          <t>2,03; 4,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,48</t>
+          <t>5,12; 8,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,64</t>
+          <t>4,62; 7,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,5</t>
+          <t>4,26; 7,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,28</t>
+          <t>2,43; 5,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,84</t>
+          <t>3,74; 7,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,3</t>
+          <t>4,59; 7,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,04</t>
+          <t>4,7; 7,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,42</t>
+          <t>2,46; 4,39</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,21</t>
+          <t>4,77; 7,21</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,3</t>
+          <t>5,02; 6,92</t>
         </is>
       </c>
     </row>
@@ -1784,27 +1784,27 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>5,39%</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,19</t>
+          <t>4,7; 6,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,18</t>
+          <t>4,51; 6,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,79</t>
+          <t>5,19; 6,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,19</t>
+          <t>5,11; 6,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,15</t>
+          <t>4,6; 6,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,13; 5,62</t>
+          <t>4,11; 5,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,28</t>
+          <t>4,61; 6,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,0; 5,58</t>
+          <t>4,8; 5,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,92</t>
+          <t>4,8; 5,91</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,57</t>
+          <t>4,51; 5,54</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,15; 6,26</t>
+          <t>5,16; 6,32</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,5; 5,74</t>
+          <t>5,1; 6,05</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16736</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28236</t>
+          <t>29381</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7990; 21196</t>
+          <t>8119; 22143</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8160; 25055</t>
+          <t>7776; 23999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7136; 20655</t>
+          <t>7058; 21481</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11015; 25453</t>
+          <t>12103; 26592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4189; 16737</t>
+          <t>3849; 15984</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8787; 25071</t>
+          <t>9052; 25199</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6632; 21972</t>
+          <t>6619; 22351</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7172; 19633</t>
+          <t>6843; 17136</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14156; 33222</t>
+          <t>14341; 32826</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21046; 44310</t>
+          <t>20530; 42927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17151; 38015</t>
+          <t>17920; 38599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20443; 39094</t>
+          <t>21467; 38975</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32144</t>
+          <t>32880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55564</t>
+          <t>57269</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23643; 47119</t>
+          <t>22138; 44640</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12316; 30436</t>
+          <t>11769; 30826</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25195; 48143</t>
+          <t>24739; 48461</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21395; 44465</t>
+          <t>22094; 45420</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17800; 37536</t>
+          <t>17461; 38044</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18130; 38249</t>
+          <t>18038; 38537</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19641; 39840</t>
+          <t>20104; 41543</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17467; 32407</t>
+          <t>17243; 32966</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44314; 76667</t>
+          <t>46523; 76192</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34498; 62000</t>
+          <t>33353; 59967</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50164; 82634</t>
+          <t>49084; 80226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43786; 71043</t>
+          <t>43663; 71362</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>44288</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8305; 22646</t>
+          <t>8155; 22167</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13014; 31934</t>
+          <t>12446; 30893</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11535; 26548</t>
+          <t>10514; 26434</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13835; 27723</t>
+          <t>13153; 27853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10788; 27016</t>
+          <t>10545; 25763</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13781; 33050</t>
+          <t>14891; 33616</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4309; 18950</t>
+          <t>4127; 17910</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17977; 32401</t>
+          <t>17457; 32825</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21541; 43356</t>
+          <t>21628; 43384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31354; 56729</t>
+          <t>30599; 57412</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18061; 39947</t>
+          <t>18429; 38922</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34893; 54974</t>
+          <t>34860; 55371</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37858</t>
+          <t>41717</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8004; 22249</t>
+          <t>8899; 23034</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18068; 40149</t>
+          <t>18634; 39777</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16970; 34846</t>
+          <t>16956; 35102</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12716; 27022</t>
+          <t>14963; 31433</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14151; 32350</t>
+          <t>13530; 30512</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12538; 30299</t>
+          <t>12084; 29192</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28790; 56691</t>
+          <t>28903; 57218</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10994; 28615</t>
+          <t>13686; 30881</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26399; 49412</t>
+          <t>26841; 48501</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35804; 61425</t>
+          <t>33498; 59979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50352; 83845</t>
+          <t>51294; 84332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26264; 50654</t>
+          <t>31730; 56690</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>16178</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9969; 25725</t>
+          <t>9638; 24927</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7748; 22796</t>
+          <t>6809; 22126</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6772; 20095</t>
+          <t>7411; 21506</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3233; 10278</t>
+          <t>3661; 11266</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5101; 18421</t>
+          <t>5476; 18148</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7670; 22243</t>
+          <t>7226; 22551</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4564; 17646</t>
+          <t>4464; 17316</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5602; 13126</t>
+          <t>6200; 13595</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17501; 37989</t>
+          <t>18325; 38536</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17984; 38664</t>
+          <t>17722; 37698</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14257; 32540</t>
+          <t>13598; 31663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10771; 21071</t>
+          <t>11438; 22878</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30394</t>
+          <t>30768</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11459; 26367</t>
+          <t>10177; 26343</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10534; 27357</t>
+          <t>11004; 26973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7207; 22534</t>
+          <t>7361; 20957</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11889; 23578</t>
+          <t>11644; 23024</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11742; 29938</t>
+          <t>11659; 30563</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11429; 29983</t>
+          <t>11581; 29357</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12864; 31352</t>
+          <t>12266; 33282</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9557; 19495</t>
+          <t>10194; 20043</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25933; 49440</t>
+          <t>26745; 50429</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27024; 49832</t>
+          <t>26766; 48677</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22719; 44720</t>
+          <t>22973; 46842</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23544; 39079</t>
+          <t>23724; 38432</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>41945</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70591</t>
+          <t>88609</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17955; 37044</t>
+          <t>17499; 36590</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31858; 58114</t>
+          <t>31819; 57348</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25289; 49545</t>
+          <t>24497; 48974</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24997; 45844</t>
+          <t>30440; 55646</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>21580; 43291</t>
+          <t>21117; 43191</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16228; 35366</t>
+          <t>15849; 35983</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15830; 37878</t>
+          <t>15632; 37337</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16864; 51633</t>
+          <t>36344; 60110</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44299; 73094</t>
+          <t>43423; 72667</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51282; 84949</t>
+          <t>53452; 85844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46233; 77624</t>
+          <t>46912; 77785</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>42702; 90320</t>
+          <t>72733; 106287</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41860</t>
+          <t>46817</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>41989</t>
+          <t>48051</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>94868</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>32081; 55810</t>
+          <t>31579; 56856</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15478; 36109</t>
+          <t>15792; 35885</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37982; 66049</t>
+          <t>39867; 68511</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16955; 61690</t>
+          <t>36891; 60311</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>31474; 58795</t>
+          <t>33371; 59433</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19681; 43370</t>
+          <t>19948; 42600</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31268; 56519</t>
+          <t>30866; 58217</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33421; 52136</t>
+          <t>38045; 58979</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70075; 107380</t>
+          <t>71778; 107619</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40300; 70691</t>
+          <t>39352; 70212</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74926; 115639</t>
+          <t>76623; 115722</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>50217; 103461</t>
+          <t>81681; 112646</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>186554</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>179530</t>
+          <t>198846</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>403079</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>153538; 202598</t>
+          <t>153862; 202443</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>155255; 211198</t>
+          <t>154266; 214229</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>174520; 230470</t>
+          <t>176028; 232086</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135483; 213993</t>
+          <t>180299; 230228</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>154493; 207824</t>
+          <t>155486; 205837</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>146419; 199323</t>
+          <t>145695; 196463</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>163587; 222624</t>
+          <t>163437; 222554</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>146292; 203907</t>
+          <t>179190; 222350</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>322063; 393925</t>
+          <t>319303; 393067</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>312413; 388024</t>
+          <t>314378; 386052</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>357015; 434160</t>
+          <t>358205; 438331</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>320204; 408796</t>
+          <t>370759; 439152</t>
         </is>
       </c>
     </row>
